--- a/artfynd/A 63570-2020 artfynd.xlsx
+++ b/artfynd/A 63570-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 63570-2020 artfynd.xlsx
+++ b/artfynd/A 63570-2020 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>73983095</v>
       </c>
       <c r="B2" t="n">
-        <v>106707</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>109171</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>574642.6944422425</v>
+        <v>574643</v>
       </c>
       <c r="R2" t="n">
-        <v>6344339.222071254</v>
+        <v>6344339</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>1977-07-20</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1977-07-20</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -799,12 +784,7 @@
         <v>74470658</v>
       </c>
       <c r="B3" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100773</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -836,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574642.6944422425</v>
+        <v>574643</v>
       </c>
       <c r="R3" t="n">
-        <v>6344339.222071254</v>
+        <v>6344339</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -869,19 +849,9 @@
           <t>1977-07-20</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1977-07-20</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -920,12 +890,7 @@
         <v>74463954</v>
       </c>
       <c r="B4" t="n">
-        <v>101692</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104061</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -953,10 +918,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574642.6944422425</v>
+        <v>574643</v>
       </c>
       <c r="R4" t="n">
-        <v>6344339.222071254</v>
+        <v>6344339</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -986,19 +951,9 @@
           <t>1977-07-20</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1977-07-20</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1037,12 +992,7 @@
         <v>74561052</v>
       </c>
       <c r="B5" t="n">
-        <v>99382</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101662</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1074,10 +1024,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>574642.6944422425</v>
+        <v>574643</v>
       </c>
       <c r="R5" t="n">
-        <v>6344339.222071254</v>
+        <v>6344339</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1107,19 +1057,9 @@
           <t>1977-07-20</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>1977-07-20</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1158,12 +1098,7 @@
         <v>74624467</v>
       </c>
       <c r="B6" t="n">
-        <v>104493</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106994</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1195,10 +1130,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>574642.6944422425</v>
+        <v>574643</v>
       </c>
       <c r="R6" t="n">
-        <v>6344339.222071254</v>
+        <v>6344339</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1228,19 +1163,9 @@
           <t>1977-07-20</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>1977-07-20</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1279,12 +1204,7 @@
         <v>74844289</v>
       </c>
       <c r="B7" t="n">
-        <v>103178</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105554</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1316,10 +1236,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>574642.6944422425</v>
+        <v>574643</v>
       </c>
       <c r="R7" t="n">
-        <v>6344339.222071254</v>
+        <v>6344339</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1349,19 +1269,9 @@
           <t>1977-07-20</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>1977-07-20</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1400,12 +1310,7 @@
         <v>74965417</v>
       </c>
       <c r="B8" t="n">
-        <v>106964</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>109435</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>574642.6944422425</v>
+        <v>574643</v>
       </c>
       <c r="R8" t="n">
-        <v>6344339.222071254</v>
+        <v>6344339</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1470,19 +1375,9 @@
           <t>1977-07-20</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>1977-07-20</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1521,12 +1416,7 @@
         <v>75061347</v>
       </c>
       <c r="B9" t="n">
-        <v>102161</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104532</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1558,10 +1448,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>574642.6944422425</v>
+        <v>574643</v>
       </c>
       <c r="R9" t="n">
-        <v>6344339.222071254</v>
+        <v>6344339</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1591,19 +1481,9 @@
           <t>1977-07-20</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>1977-07-20</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1642,12 +1522,7 @@
         <v>75157994</v>
       </c>
       <c r="B10" t="n">
-        <v>99590</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101877</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1679,10 +1554,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>574642.6944422425</v>
+        <v>574643</v>
       </c>
       <c r="R10" t="n">
-        <v>6344339.222071254</v>
+        <v>6344339</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1712,19 +1587,9 @@
           <t>1977-07-20</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>1977-07-20</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">

--- a/artfynd/A 63570-2020 artfynd.xlsx
+++ b/artfynd/A 63570-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73983095</v>
       </c>
       <c r="B2" t="n">
-        <v>109171</v>
+        <v>109180</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>74470658</v>
       </c>
       <c r="B3" t="n">
-        <v>100773</v>
+        <v>100779</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>74463954</v>
       </c>
       <c r="B4" t="n">
-        <v>104061</v>
+        <v>104070</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>74561052</v>
       </c>
       <c r="B5" t="n">
-        <v>101662</v>
+        <v>101668</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>74624467</v>
       </c>
       <c r="B6" t="n">
-        <v>106994</v>
+        <v>107003</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         <v>74844289</v>
       </c>
       <c r="B7" t="n">
-        <v>105554</v>
+        <v>105563</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>74965417</v>
       </c>
       <c r="B8" t="n">
-        <v>109435</v>
+        <v>109444</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>75061347</v>
       </c>
       <c r="B9" t="n">
-        <v>104532</v>
+        <v>104541</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>75157994</v>
       </c>
       <c r="B10" t="n">
-        <v>101877</v>
+        <v>101883</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 63570-2020 artfynd.xlsx
+++ b/artfynd/A 63570-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73983095</v>
       </c>
       <c r="B2" t="n">
-        <v>109180</v>
+        <v>109185</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>74470658</v>
       </c>
       <c r="B3" t="n">
-        <v>100779</v>
+        <v>100780</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>74463954</v>
       </c>
       <c r="B4" t="n">
-        <v>104070</v>
+        <v>104073</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>74561052</v>
       </c>
       <c r="B5" t="n">
-        <v>101668</v>
+        <v>101669</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>74624467</v>
       </c>
       <c r="B6" t="n">
-        <v>107003</v>
+        <v>107008</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         <v>74844289</v>
       </c>
       <c r="B7" t="n">
-        <v>105563</v>
+        <v>105566</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>74965417</v>
       </c>
       <c r="B8" t="n">
-        <v>109444</v>
+        <v>109449</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>75061347</v>
       </c>
       <c r="B9" t="n">
-        <v>104541</v>
+        <v>104544</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>75157994</v>
       </c>
       <c r="B10" t="n">
-        <v>101883</v>
+        <v>101884</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 63570-2020 artfynd.xlsx
+++ b/artfynd/A 63570-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73983095</v>
       </c>
       <c r="B2" t="n">
-        <v>109185</v>
+        <v>109213</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>74470658</v>
       </c>
       <c r="B3" t="n">
-        <v>100780</v>
+        <v>100807</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>74463954</v>
       </c>
       <c r="B4" t="n">
-        <v>104073</v>
+        <v>104100</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>74561052</v>
       </c>
       <c r="B5" t="n">
-        <v>101669</v>
+        <v>101696</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>74624467</v>
       </c>
       <c r="B6" t="n">
-        <v>107008</v>
+        <v>107036</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         <v>74844289</v>
       </c>
       <c r="B7" t="n">
-        <v>105566</v>
+        <v>105594</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>74965417</v>
       </c>
       <c r="B8" t="n">
-        <v>109449</v>
+        <v>109477</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>75061347</v>
       </c>
       <c r="B9" t="n">
-        <v>104544</v>
+        <v>104571</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>75157994</v>
       </c>
       <c r="B10" t="n">
-        <v>101884</v>
+        <v>101911</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 63570-2020 artfynd.xlsx
+++ b/artfynd/A 63570-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73983095</v>
       </c>
       <c r="B2" t="n">
-        <v>109213</v>
+        <v>109219</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>74470658</v>
       </c>
       <c r="B3" t="n">
-        <v>100807</v>
+        <v>100813</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>74463954</v>
       </c>
       <c r="B4" t="n">
-        <v>104100</v>
+        <v>104106</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>74561052</v>
       </c>
       <c r="B5" t="n">
-        <v>101696</v>
+        <v>101702</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>74624467</v>
       </c>
       <c r="B6" t="n">
-        <v>107036</v>
+        <v>107042</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         <v>74844289</v>
       </c>
       <c r="B7" t="n">
-        <v>105594</v>
+        <v>105600</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>74965417</v>
       </c>
       <c r="B8" t="n">
-        <v>109477</v>
+        <v>109483</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>75061347</v>
       </c>
       <c r="B9" t="n">
-        <v>104571</v>
+        <v>104577</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>75157994</v>
       </c>
       <c r="B10" t="n">
-        <v>101911</v>
+        <v>101917</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 63570-2020 artfynd.xlsx
+++ b/artfynd/A 63570-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73983095</v>
       </c>
       <c r="B2" t="n">
-        <v>109219</v>
+        <v>109226</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>74470658</v>
       </c>
       <c r="B3" t="n">
-        <v>100813</v>
+        <v>100820</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>74463954</v>
       </c>
       <c r="B4" t="n">
-        <v>104106</v>
+        <v>104113</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>74561052</v>
       </c>
       <c r="B5" t="n">
-        <v>101702</v>
+        <v>101709</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>74624467</v>
       </c>
       <c r="B6" t="n">
-        <v>107042</v>
+        <v>107049</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         <v>74844289</v>
       </c>
       <c r="B7" t="n">
-        <v>105600</v>
+        <v>105607</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>74965417</v>
       </c>
       <c r="B8" t="n">
-        <v>109483</v>
+        <v>109490</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>75061347</v>
       </c>
       <c r="B9" t="n">
-        <v>104577</v>
+        <v>104584</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>75157994</v>
       </c>
       <c r="B10" t="n">
-        <v>101917</v>
+        <v>101924</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 63570-2020 artfynd.xlsx
+++ b/artfynd/A 63570-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73983095</v>
       </c>
       <c r="B2" t="n">
-        <v>109226</v>
+        <v>109230</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>74470658</v>
       </c>
       <c r="B3" t="n">
-        <v>100820</v>
+        <v>100824</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>74463954</v>
       </c>
       <c r="B4" t="n">
-        <v>104113</v>
+        <v>104117</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>74561052</v>
       </c>
       <c r="B5" t="n">
-        <v>101709</v>
+        <v>101713</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>74624467</v>
       </c>
       <c r="B6" t="n">
-        <v>107049</v>
+        <v>107053</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         <v>74844289</v>
       </c>
       <c r="B7" t="n">
-        <v>105607</v>
+        <v>105611</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>74965417</v>
       </c>
       <c r="B8" t="n">
-        <v>109490</v>
+        <v>109494</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>75061347</v>
       </c>
       <c r="B9" t="n">
-        <v>104584</v>
+        <v>104588</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>75157994</v>
       </c>
       <c r="B10" t="n">
-        <v>101924</v>
+        <v>101928</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 63570-2020 artfynd.xlsx
+++ b/artfynd/A 63570-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73983095</v>
       </c>
       <c r="B2" t="n">
-        <v>109230</v>
+        <v>109238</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>74470658</v>
       </c>
       <c r="B3" t="n">
-        <v>100824</v>
+        <v>100831</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>74463954</v>
       </c>
       <c r="B4" t="n">
-        <v>104117</v>
+        <v>104124</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>74561052</v>
       </c>
       <c r="B5" t="n">
-        <v>101713</v>
+        <v>101720</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>74624467</v>
       </c>
       <c r="B6" t="n">
-        <v>107053</v>
+        <v>107061</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         <v>74844289</v>
       </c>
       <c r="B7" t="n">
-        <v>105611</v>
+        <v>105618</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>74965417</v>
       </c>
       <c r="B8" t="n">
-        <v>109494</v>
+        <v>109502</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>75061347</v>
       </c>
       <c r="B9" t="n">
-        <v>104588</v>
+        <v>104595</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>75157994</v>
       </c>
       <c r="B10" t="n">
-        <v>101928</v>
+        <v>101935</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 63570-2020 artfynd.xlsx
+++ b/artfynd/A 63570-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73983095</v>
       </c>
       <c r="B2" t="n">
-        <v>109241</v>
+        <v>109246</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>74470658</v>
       </c>
       <c r="B3" t="n">
-        <v>100834</v>
+        <v>100839</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>74463954</v>
       </c>
       <c r="B4" t="n">
-        <v>104127</v>
+        <v>104132</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>74561052</v>
       </c>
       <c r="B5" t="n">
-        <v>101723</v>
+        <v>101728</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>74624467</v>
       </c>
       <c r="B6" t="n">
-        <v>107064</v>
+        <v>107069</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         <v>74844289</v>
       </c>
       <c r="B7" t="n">
-        <v>105621</v>
+        <v>105626</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>74965417</v>
       </c>
       <c r="B8" t="n">
-        <v>109505</v>
+        <v>109510</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>75061347</v>
       </c>
       <c r="B9" t="n">
-        <v>104598</v>
+        <v>104603</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>75157994</v>
       </c>
       <c r="B10" t="n">
-        <v>101938</v>
+        <v>101943</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 63570-2020 artfynd.xlsx
+++ b/artfynd/A 63570-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73983095</v>
       </c>
       <c r="B2" t="n">
-        <v>109246</v>
+        <v>109254</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>74470658</v>
       </c>
       <c r="B3" t="n">
-        <v>100839</v>
+        <v>100847</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>74463954</v>
       </c>
       <c r="B4" t="n">
-        <v>104132</v>
+        <v>104140</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>74561052</v>
       </c>
       <c r="B5" t="n">
-        <v>101728</v>
+        <v>101736</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>74624467</v>
       </c>
       <c r="B6" t="n">
-        <v>107069</v>
+        <v>107077</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         <v>74844289</v>
       </c>
       <c r="B7" t="n">
-        <v>105626</v>
+        <v>105634</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>74965417</v>
       </c>
       <c r="B8" t="n">
-        <v>109510</v>
+        <v>109518</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>75061347</v>
       </c>
       <c r="B9" t="n">
-        <v>104603</v>
+        <v>104611</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>75157994</v>
       </c>
       <c r="B10" t="n">
-        <v>101943</v>
+        <v>101951</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 63570-2020 artfynd.xlsx
+++ b/artfynd/A 63570-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73983095</v>
       </c>
       <c r="B2" t="n">
-        <v>109254</v>
+        <v>109264</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>74470658</v>
       </c>
       <c r="B3" t="n">
-        <v>100847</v>
+        <v>100857</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>74463954</v>
       </c>
       <c r="B4" t="n">
-        <v>104140</v>
+        <v>104150</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>74561052</v>
       </c>
       <c r="B5" t="n">
-        <v>101736</v>
+        <v>101746</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>74624467</v>
       </c>
       <c r="B6" t="n">
-        <v>107077</v>
+        <v>107087</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         <v>74844289</v>
       </c>
       <c r="B7" t="n">
-        <v>105634</v>
+        <v>105644</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>74965417</v>
       </c>
       <c r="B8" t="n">
-        <v>109518</v>
+        <v>109528</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>75061347</v>
       </c>
       <c r="B9" t="n">
-        <v>104611</v>
+        <v>104621</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>75157994</v>
       </c>
       <c r="B10" t="n">
-        <v>101951</v>
+        <v>101961</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
